--- a/designs/三英战吕布_关卡设计.xlsx
+++ b/designs/三英战吕布_关卡设计.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,16 +29,26 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00000000"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D4A84B"/>
+        <bgColor rgb="00D4A84B"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -46,12 +56,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,32 +440,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>关卡名称</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>关卡类型</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>关卡ID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>关卡等级</t>
         </is>
@@ -464,10 +487,8 @@
           <t>S240001</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+      <c r="D2" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -525,39 +546,33 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>我方流程</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
           <t>开局演绎</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>刘备、关羽、张飞三兄弟联手对抗吕布，玩家控制三人，体验配合攻击。4回合后触发剧情，三兄弟败退。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>第二阶段：燎原火登场</t>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>刘备、关羽、张飞三兄弟联手对抗吕布，玩家控制三人，体验配合攻击。4回合后触发剧情，三兄弟败退，燎原火登场。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>甲板上流程</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
+          <t>第二阶段：燎原火登场</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>燎原火单骑救场</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>燎原火（赵云）单骑救场，与吕布一对一单挑。6回合后触发撤退剧情，关卡结束。</t>
         </is>
@@ -577,735 +592,735 @@
   <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>镜头\动作</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>角色</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>配音</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>character</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>boxes</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>spine</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>L\R</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>bgL</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>bgR</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>虎牢关全景</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>黑云压城，战鼓雷鸣</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>城门打开</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>吕布</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>关东鼠辈，谁敢与我一战！</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>赤兔马嘶鸣</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>分镜特写</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>张飞</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>燕人张飞在此！</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>丈八蛇矛指向吕布</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>三人并立</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>关羽</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>大哥，三弟，今日便让吕布见识桃园之义！</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>青龙偃月刀出鞘</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>刘备拔剑</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>刘备</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>为了天下苍生，战！</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>双股剑交叉</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>吕布冷笑</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>吕布</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>三个一起上？有意思。</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>方天画戟横举</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr"/>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>【第3回合触发】</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>吕布反击</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>吕布</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>就这点本事？</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>击退张飞</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>关羽支援</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>关羽</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>三弟！大哥，变阵！</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>挡住吕布追击</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>刘备辅助</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>刘备</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>云长小心！</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>给关羽加血</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr"/>
+      <c r="C13" s="2" t="inlineStr"/>
+      <c r="D13" s="2" t="inlineStr"/>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>【第4回合触发】</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr"/>
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>三人后退</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>张飞</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>可恶...这厮太强了...</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>单膝跪地</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>吕布逼近</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>吕布</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>还没完呢。</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>赤兔马踏步</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>白影闪过</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>燎原火</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>够了。</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>银枪挡住画戟</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>分镜特写</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>燎原火</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>你的对手，换人了。</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>摘下面具</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>吕布惊讶</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>吕布</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>你是...那个残兵？</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>认出燎原火</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>燎原火</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>燎原火</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>燎原火，领教奉先高招。</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>龙胆亮银枪旋转</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr"/>
+      <c r="C21" s="2" t="inlineStr"/>
+      <c r="D21" s="2" t="inlineStr"/>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>【第6回合触发】</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr"/>
+      <c r="C22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>双方后退</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>吕布</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>能接我三十招的，你是第二个。</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>画戟滴血</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+      <c r="E23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>燎原火</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>燎原火</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>第一个是谁？</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>银枪斜指</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>吕布</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>吕布</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>你自己去问董卓吧。</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>冷笑</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+      <c r="E25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>号角声</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>关东军撤退信号</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>燎原火</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>燎原火</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>今天就到这里。</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>收枪</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>吕布</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>吕布</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>下次，你不会这么幸运。</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>目送离开</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1318,965 +1333,1560 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P31"/>
+  <dimension ref="A1:AC33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="4" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="9" max="9"/>
+    <col width="4" customWidth="1" min="10" max="10"/>
+    <col width="4" customWidth="1" min="11" max="11"/>
+    <col width="4" customWidth="1" min="12" max="12"/>
+    <col width="4" customWidth="1" min="13" max="13"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="18" max="18"/>
+    <col width="4" customWidth="1" min="19" max="19"/>
+    <col width="4" customWidth="1" min="20" max="20"/>
+    <col width="4" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="6" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="24" max="24"/>
+    <col width="6" customWidth="1" min="25" max="25"/>
+    <col width="6" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="27" max="27"/>
+    <col width="10" customWidth="1" min="28" max="28"/>
+    <col width="6" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>关卡信息 &gt;&gt;&gt;</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>关卡名称</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>三英战吕布</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>关卡备注</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>S240001</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>场景编号</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>初始摄像机</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>等级</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>上阵</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>回合</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>宝箱</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>关卡编号</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>2010300</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>胜利条件</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>坚持4回合（第一阶段）/ 坚持6回合或吕布血量≤30%（第二阶段）</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>坚持4回合（一阶段）/坚持6回合或吕布血量≤30%（二阶段）</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>二阶段胜利条件</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>失败条件</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>我方全灭</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>二阶段失败条件</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="B5" s="4" t="inlineStr"/>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>城墙</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>城墙</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>城墙</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>城门</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>城墙</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>城墙</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
+      <c r="J5" s="4" t="inlineStr"/>
+      <c r="K5" s="4" t="inlineStr"/>
+      <c r="L5" s="4" t="inlineStr"/>
+      <c r="M5" s="4" t="inlineStr"/>
+      <c r="N5" s="4" t="inlineStr"/>
+      <c r="O5" s="4" t="inlineStr"/>
+      <c r="P5" s="4" t="inlineStr"/>
+      <c r="Q5" s="4" t="inlineStr"/>
+      <c r="R5" s="4" t="inlineStr"/>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>上阵角色信息</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr"/>
+      <c r="X5" s="3" t="inlineStr"/>
+      <c r="Y5" s="3" t="inlineStr"/>
+      <c r="Z5" s="3" t="inlineStr"/>
+      <c r="AA5" s="3" t="inlineStr"/>
+      <c r="AB5" s="3" t="inlineStr"/>
+      <c r="AC5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="4" t="inlineStr"/>
+      <c r="D6" s="4" t="inlineStr"/>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="inlineStr"/>
+      <c r="K6" s="4" t="inlineStr"/>
+      <c r="L6" s="4" t="inlineStr"/>
+      <c r="M6" s="4" t="inlineStr"/>
+      <c r="N6" s="4" t="inlineStr"/>
+      <c r="O6" s="4" t="inlineStr"/>
+      <c r="P6" s="4" t="inlineStr"/>
+      <c r="Q6" s="4" t="inlineStr"/>
+      <c r="R6" s="4" t="inlineStr"/>
+      <c r="V6" s="1" t="inlineStr">
+        <is>
+          <t>地图标识</t>
+        </is>
+      </c>
+      <c r="W6" s="1" t="inlineStr">
+        <is>
+          <t>朝向</t>
+        </is>
+      </c>
+      <c r="X6" s="1" t="inlineStr">
+        <is>
+          <t>角色实例</t>
+        </is>
+      </c>
+      <c r="Y6" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="Z6" s="1" t="inlineStr">
+        <is>
+          <t>等级</t>
+        </is>
+      </c>
+      <c r="AA6" s="1" t="inlineStr">
+        <is>
+          <t>血量</t>
+        </is>
+      </c>
+      <c r="AB6" s="1" t="inlineStr">
+        <is>
+          <t>行为树</t>
+        </is>
+      </c>
+      <c r="AC6" s="1" t="inlineStr">
+        <is>
+          <t>队伍</t>
+        </is>
+      </c>
+    </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>上阵角色信息</t>
+      <c r="B7" s="4" t="inlineStr"/>
+      <c r="C7" s="4" t="inlineStr"/>
+      <c r="D7" s="4" t="inlineStr"/>
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>布</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" s="4" t="inlineStr"/>
+      <c r="J7" s="4" t="inlineStr"/>
+      <c r="K7" s="4" t="inlineStr"/>
+      <c r="L7" s="4" t="inlineStr"/>
+      <c r="M7" s="4" t="inlineStr"/>
+      <c r="N7" s="4" t="inlineStr"/>
+      <c r="O7" s="4" t="inlineStr"/>
+      <c r="P7" s="4" t="inlineStr"/>
+      <c r="Q7" s="4" t="inlineStr"/>
+      <c r="R7" s="4" t="inlineStr"/>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>右</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>燎原火（赵云）</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>22000</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>刺客型</t>
+        </is>
+      </c>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr"/>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr"/>
+      <c r="J8" s="4" t="inlineStr"/>
+      <c r="K8" s="4" t="inlineStr"/>
+      <c r="L8" s="4" t="inlineStr"/>
+      <c r="M8" s="4" t="inlineStr"/>
+      <c r="N8" s="4" t="inlineStr"/>
+      <c r="O8" s="4" t="inlineStr"/>
+      <c r="P8" s="4" t="inlineStr"/>
+      <c r="Q8" s="4" t="inlineStr"/>
+      <c r="R8" s="4" t="inlineStr"/>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>备</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>右</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>刘备</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>15000</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>支援型</t>
+        </is>
+      </c>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="4" t="inlineStr"/>
+      <c r="C9" s="4" t="inlineStr"/>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>盾1</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>盾2</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>骑1</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>骑2</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>盾3</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
+      <c r="J9" s="4" t="inlineStr"/>
+      <c r="K9" s="4" t="inlineStr"/>
+      <c r="L9" s="4" t="inlineStr"/>
+      <c r="M9" s="4" t="inlineStr"/>
+      <c r="N9" s="4" t="inlineStr"/>
+      <c r="O9" s="4" t="inlineStr"/>
+      <c r="P9" s="4" t="inlineStr"/>
+      <c r="Q9" s="4" t="inlineStr"/>
+      <c r="R9" s="4" t="inlineStr"/>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>羽</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>右</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>关羽</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>18000</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>攻击型</t>
+        </is>
+      </c>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="4" t="inlineStr"/>
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr"/>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" s="4" t="inlineStr"/>
+      <c r="J10" s="4" t="inlineStr"/>
+      <c r="K10" s="4" t="inlineStr"/>
+      <c r="L10" s="4" t="inlineStr"/>
+      <c r="M10" s="4" t="inlineStr"/>
+      <c r="N10" s="4" t="inlineStr"/>
+      <c r="O10" s="4" t="inlineStr"/>
+      <c r="P10" s="4" t="inlineStr"/>
+      <c r="Q10" s="4" t="inlineStr"/>
+      <c r="R10" s="4" t="inlineStr"/>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>飞</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>右</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>张飞</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>20000</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>防御型</t>
+        </is>
+      </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="4" t="inlineStr"/>
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr"/>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr"/>
+      <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" s="4" t="inlineStr"/>
+      <c r="J11" s="4" t="inlineStr"/>
+      <c r="K11" s="4" t="inlineStr"/>
+      <c r="L11" s="4" t="inlineStr"/>
+      <c r="M11" s="4" t="inlineStr"/>
+      <c r="N11" s="4" t="inlineStr"/>
+      <c r="O11" s="4" t="inlineStr"/>
+      <c r="P11" s="4" t="inlineStr"/>
+      <c r="Q11" s="4" t="inlineStr"/>
+      <c r="R11" s="4" t="inlineStr"/>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>布</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>左</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>吕布</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>50000</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>BOSS型</t>
+        </is>
+      </c>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="4" t="inlineStr"/>
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr"/>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr"/>
+      <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr"/>
+      <c r="I12" s="4" t="inlineStr"/>
+      <c r="J12" s="4" t="inlineStr"/>
+      <c r="K12" s="4" t="inlineStr"/>
+      <c r="L12" s="4" t="inlineStr"/>
+      <c r="M12" s="4" t="inlineStr"/>
+      <c r="N12" s="4" t="inlineStr"/>
+      <c r="O12" s="4" t="inlineStr"/>
+      <c r="P12" s="4" t="inlineStr"/>
+      <c r="Q12" s="4" t="inlineStr"/>
+      <c r="R12" s="4" t="inlineStr"/>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>骑1</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>左</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>并州铁骑</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>12000</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>骑兵型</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="4" t="inlineStr"/>
+      <c r="C13" s="4" t="inlineStr"/>
+      <c r="D13" s="4" t="inlineStr"/>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr"/>
+      <c r="G13" s="4" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr"/>
+      <c r="I13" s="4" t="inlineStr"/>
+      <c r="J13" s="4" t="inlineStr"/>
+      <c r="K13" s="4" t="inlineStr"/>
+      <c r="L13" s="4" t="inlineStr"/>
+      <c r="M13" s="4" t="inlineStr"/>
+      <c r="N13" s="4" t="inlineStr"/>
+      <c r="O13" s="4" t="inlineStr"/>
+      <c r="P13" s="4" t="inlineStr"/>
+      <c r="Q13" s="4" t="inlineStr"/>
+      <c r="R13" s="4" t="inlineStr"/>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>骑2</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>左</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>并州铁骑</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>12000</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>骑兵型</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="4" t="inlineStr"/>
+      <c r="C14" s="4" t="inlineStr"/>
+      <c r="D14" s="4" t="inlineStr"/>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr"/>
+      <c r="G14" s="4" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr"/>
+      <c r="I14" s="4" t="inlineStr"/>
+      <c r="J14" s="4" t="inlineStr"/>
+      <c r="K14" s="4" t="inlineStr"/>
+      <c r="L14" s="4" t="inlineStr"/>
+      <c r="M14" s="4" t="inlineStr"/>
+      <c r="N14" s="4" t="inlineStr"/>
+      <c r="O14" s="4" t="inlineStr"/>
+      <c r="P14" s="4" t="inlineStr"/>
+      <c r="Q14" s="4" t="inlineStr"/>
+      <c r="R14" s="4" t="inlineStr"/>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>骑3</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>左</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>并州铁骑</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>12000</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>骑兵型</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="4" t="inlineStr"/>
+      <c r="C15" s="4" t="inlineStr"/>
+      <c r="D15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" s="4" t="inlineStr"/>
+      <c r="J15" s="4" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr"/>
+      <c r="L15" s="4" t="inlineStr"/>
+      <c r="M15" s="4" t="inlineStr"/>
+      <c r="N15" s="4" t="inlineStr"/>
+      <c r="O15" s="4" t="inlineStr"/>
+      <c r="P15" s="4" t="inlineStr"/>
+      <c r="Q15" s="4" t="inlineStr"/>
+      <c r="R15" s="4" t="inlineStr"/>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>骑4</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>左</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>并州铁骑</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>12000</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>骑兵型</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4" t="inlineStr"/>
+      <c r="D16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr"/>
+      <c r="G16" s="4" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr"/>
+      <c r="I16" s="4" t="inlineStr"/>
+      <c r="J16" s="4" t="inlineStr"/>
+      <c r="K16" s="4" t="inlineStr"/>
+      <c r="L16" s="4" t="inlineStr"/>
+      <c r="M16" s="4" t="inlineStr"/>
+      <c r="N16" s="4" t="inlineStr"/>
+      <c r="O16" s="4" t="inlineStr"/>
+      <c r="P16" s="4" t="inlineStr"/>
+      <c r="Q16" s="4" t="inlineStr"/>
+      <c r="R16" s="4" t="inlineStr"/>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>盾1</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>左</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>陷阵营盾卫</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>15000</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>坦克型</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="4" t="inlineStr"/>
+      <c r="C17" s="4" t="inlineStr"/>
+      <c r="D17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr"/>
+      <c r="G17" s="4" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" s="4" t="inlineStr"/>
+      <c r="J17" s="4" t="inlineStr"/>
+      <c r="K17" s="4" t="inlineStr"/>
+      <c r="L17" s="4" t="inlineStr"/>
+      <c r="M17" s="4" t="inlineStr"/>
+      <c r="N17" s="4" t="inlineStr"/>
+      <c r="O17" s="4" t="inlineStr"/>
+      <c r="P17" s="4" t="inlineStr"/>
+      <c r="Q17" s="4" t="inlineStr"/>
+      <c r="R17" s="4" t="inlineStr"/>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>盾2</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>左</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>陷阵营盾卫</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>15000</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>坦克型</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="4" t="inlineStr"/>
+      <c r="C18" s="4" t="inlineStr"/>
+      <c r="D18" s="4" t="inlineStr"/>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr"/>
+      <c r="G18" s="4" t="inlineStr"/>
+      <c r="H18" s="4" t="inlineStr"/>
+      <c r="I18" s="4" t="inlineStr"/>
+      <c r="J18" s="4" t="inlineStr"/>
+      <c r="K18" s="4" t="inlineStr"/>
+      <c r="L18" s="4" t="inlineStr"/>
+      <c r="M18" s="4" t="inlineStr"/>
+      <c r="N18" s="4" t="inlineStr"/>
+      <c r="O18" s="4" t="inlineStr"/>
+      <c r="P18" s="4" t="inlineStr"/>
+      <c r="Q18" s="4" t="inlineStr"/>
+      <c r="R18" s="4" t="inlineStr"/>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>盾3</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>左</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>陷阵营盾卫</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>15000</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>坦克型</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="4" t="inlineStr"/>
+      <c r="C19" s="4" t="inlineStr"/>
+      <c r="D19" s="4" t="inlineStr"/>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr"/>
+      <c r="G19" s="4" t="inlineStr"/>
+      <c r="H19" s="4" t="inlineStr"/>
+      <c r="I19" s="4" t="inlineStr"/>
+      <c r="J19" s="4" t="inlineStr"/>
+      <c r="K19" s="4" t="inlineStr"/>
+      <c r="L19" s="4" t="inlineStr"/>
+      <c r="M19" s="4" t="inlineStr"/>
+      <c r="N19" s="4" t="inlineStr"/>
+      <c r="O19" s="4" t="inlineStr"/>
+      <c r="P19" s="4" t="inlineStr"/>
+      <c r="Q19" s="4" t="inlineStr"/>
+      <c r="R19" s="4" t="inlineStr"/>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>盾4</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>左</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>陷阵营盾卫</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>15000</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>坦克型</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="4" t="inlineStr"/>
+      <c r="C20" s="4" t="inlineStr"/>
+      <c r="D20" s="4" t="inlineStr"/>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr"/>
+      <c r="G20" s="4" t="inlineStr"/>
+      <c r="H20" s="4" t="inlineStr"/>
+      <c r="I20" s="4" t="inlineStr"/>
+      <c r="J20" s="4" t="inlineStr"/>
+      <c r="K20" s="4" t="inlineStr"/>
+      <c r="L20" s="4" t="inlineStr"/>
+      <c r="M20" s="4" t="inlineStr"/>
+      <c r="N20" s="4" t="inlineStr"/>
+      <c r="O20" s="4" t="inlineStr"/>
+      <c r="P20" s="4" t="inlineStr"/>
+      <c r="Q20" s="4" t="inlineStr"/>
+      <c r="R20" s="4" t="inlineStr"/>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>射1</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>左</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>并州弓骑</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>射手型</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="4" t="inlineStr"/>
+      <c r="C21" s="4" t="inlineStr"/>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>飞</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr"/>
+      <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="4" t="inlineStr"/>
+      <c r="J21" s="4" t="inlineStr"/>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>羽</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr"/>
+      <c r="M21" s="4" t="inlineStr"/>
+      <c r="N21" s="4" t="inlineStr"/>
+      <c r="O21" s="4" t="inlineStr"/>
+      <c r="P21" s="4" t="inlineStr"/>
+      <c r="Q21" s="4" t="inlineStr"/>
+      <c r="R21" s="4" t="inlineStr"/>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>射2</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>左</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>并州弓骑</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>射手型</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="4" t="inlineStr"/>
+      <c r="C22" s="4" t="inlineStr"/>
+      <c r="D22" s="4" t="inlineStr"/>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr"/>
+      <c r="G22" s="4" t="inlineStr"/>
+      <c r="H22" s="4" t="inlineStr"/>
+      <c r="I22" s="4" t="inlineStr"/>
+      <c r="J22" s="4" t="inlineStr"/>
+      <c r="K22" s="4" t="inlineStr"/>
+      <c r="L22" s="4" t="inlineStr"/>
+      <c r="M22" s="4" t="inlineStr"/>
+      <c r="N22" s="4" t="inlineStr"/>
+      <c r="O22" s="4" t="inlineStr"/>
+      <c r="P22" s="4" t="inlineStr"/>
+      <c r="Q22" s="4" t="inlineStr"/>
+      <c r="R22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="4" t="inlineStr"/>
+      <c r="C23" s="4" t="inlineStr"/>
+      <c r="D23" s="4" t="inlineStr"/>
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr"/>
+      <c r="G23" s="4" t="inlineStr"/>
+      <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" s="4" t="inlineStr"/>
+      <c r="J23" s="4" t="inlineStr"/>
+      <c r="K23" s="4" t="inlineStr"/>
+      <c r="L23" s="4" t="inlineStr"/>
+      <c r="M23" s="4" t="inlineStr"/>
+      <c r="N23" s="4" t="inlineStr"/>
+      <c r="O23" s="4" t="inlineStr"/>
+      <c r="P23" s="4" t="inlineStr"/>
+      <c r="Q23" s="4" t="inlineStr"/>
+      <c r="R23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="4" t="inlineStr"/>
+      <c r="C24" s="4" t="inlineStr"/>
+      <c r="D24" s="4" t="inlineStr"/>
+      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr"/>
+      <c r="G24" s="4" t="inlineStr"/>
+      <c r="H24" s="4" t="inlineStr"/>
+      <c r="I24" s="4" t="inlineStr"/>
+      <c r="J24" s="4" t="inlineStr"/>
+      <c r="K24" s="4" t="inlineStr"/>
+      <c r="L24" s="4" t="inlineStr"/>
+      <c r="M24" s="4" t="inlineStr"/>
+      <c r="N24" s="4" t="inlineStr"/>
+      <c r="O24" s="4" t="inlineStr"/>
+      <c r="P24" s="4" t="inlineStr"/>
+      <c r="Q24" s="4" t="inlineStr"/>
+      <c r="R24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="4" t="inlineStr"/>
+      <c r="C25" s="4" t="inlineStr"/>
+      <c r="D25" s="4" t="inlineStr"/>
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr"/>
+      <c r="G25" s="4" t="inlineStr"/>
+      <c r="H25" s="4" t="inlineStr"/>
+      <c r="I25" s="4" t="inlineStr"/>
+      <c r="J25" s="4" t="inlineStr"/>
+      <c r="K25" s="4" t="inlineStr"/>
+      <c r="L25" s="4" t="inlineStr"/>
+      <c r="M25" s="4" t="inlineStr"/>
+      <c r="N25" s="4" t="inlineStr"/>
+      <c r="O25" s="4" t="inlineStr"/>
+      <c r="P25" s="4" t="inlineStr"/>
+      <c r="Q25" s="4" t="inlineStr"/>
+      <c r="R25" s="4" t="inlineStr"/>
+      <c r="V25" s="5" t="inlineStr">
+        <is>
+          <t>地形角色信息</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="4" t="inlineStr"/>
+      <c r="C26" s="4" t="inlineStr"/>
+      <c r="D26" s="4" t="inlineStr"/>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr"/>
+      <c r="G26" s="4" t="inlineStr"/>
+      <c r="H26" s="4" t="inlineStr"/>
+      <c r="I26" s="4" t="inlineStr"/>
+      <c r="J26" s="4" t="inlineStr"/>
+      <c r="K26" s="4" t="inlineStr"/>
+      <c r="L26" s="4" t="inlineStr"/>
+      <c r="M26" s="4" t="inlineStr"/>
+      <c r="N26" s="4" t="inlineStr"/>
+      <c r="O26" s="4" t="inlineStr"/>
+      <c r="P26" s="4" t="inlineStr"/>
+      <c r="Q26" s="4" t="inlineStr"/>
+      <c r="R26" s="4" t="inlineStr"/>
+      <c r="V26" s="1" t="inlineStr">
         <is>
           <t>地图标识</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>朝向</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>角色实例</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+      <c r="W26" s="1" t="inlineStr">
+        <is>
+          <t>机关实例</t>
+        </is>
+      </c>
+      <c r="X26" s="1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>等级</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>血量</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>行为树</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>队伍</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="Y26" s="1" t="inlineStr">
+        <is>
+          <t>效果说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="4" t="inlineStr"/>
+      <c r="C27" s="4" t="inlineStr"/>
+      <c r="D27" s="4" t="inlineStr"/>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr"/>
+      <c r="G27" s="4" t="inlineStr"/>
+      <c r="H27" s="4" t="inlineStr"/>
+      <c r="I27" s="4" t="inlineStr"/>
+      <c r="J27" s="4" t="inlineStr"/>
+      <c r="K27" s="4" t="inlineStr"/>
+      <c r="L27" s="4" t="inlineStr"/>
+      <c r="M27" s="4" t="inlineStr"/>
+      <c r="N27" s="4" t="inlineStr"/>
+      <c r="O27" s="4" t="inlineStr"/>
+      <c r="P27" s="4" t="inlineStr"/>
+      <c r="Q27" s="4" t="inlineStr"/>
+      <c r="R27" s="4" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>城墙</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>城墙地形</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>801</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>防御+5，不可穿越</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="4" t="inlineStr"/>
+      <c r="C28" s="4" t="inlineStr"/>
+      <c r="D28" s="4" t="inlineStr"/>
+      <c r="E28" s="4" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr"/>
+      <c r="G28" s="4" t="inlineStr"/>
+      <c r="H28" s="4" t="inlineStr"/>
+      <c r="I28" s="4" t="inlineStr"/>
+      <c r="J28" s="4" t="inlineStr"/>
+      <c r="K28" s="4" t="inlineStr"/>
+      <c r="L28" s="4" t="inlineStr"/>
+      <c r="M28" s="4" t="inlineStr"/>
+      <c r="N28" s="4" t="inlineStr"/>
+      <c r="O28" s="4" t="inlineStr"/>
+      <c r="P28" s="4" t="inlineStr"/>
+      <c r="Q28" s="4" t="inlineStr"/>
+      <c r="R28" s="4" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>城门</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>城门机关</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>802</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>第4回合打开，吕布可召唤增援</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="4" t="inlineStr"/>
+      <c r="C29" s="4" t="inlineStr"/>
+      <c r="D29" s="4" t="inlineStr"/>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>备</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>上</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>刘备</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>15000</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>支援型</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>羽</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>上</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>关羽</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>18000</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>攻击型</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>飞</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>上</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>张飞</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>20000</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>防御型</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>火</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>上</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>燎原火（赵云）</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>22000</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>刺客型</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>布</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>下</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>吕布</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>50000</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>BOSS型</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>骑1</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>下</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>并州铁骑</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>12000</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>骑兵型</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>骑2</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>下</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>并州铁骑</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>12000</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>骑兵型</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>骑3</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>下</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>并州铁骑</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>12000</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>骑兵型</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>骑4</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>下</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>并州铁骑</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>12000</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>骑兵型</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>盾1</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>下</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>陷阵营盾卫</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>15000</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>坦克型</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>盾2</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>下</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>陷阵营盾卫</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>15000</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>坦克型</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>盾3</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>下</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>陷阵营盾卫</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>15000</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>坦克型</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>盾4</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>下</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>陷阵营盾卫</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>15000</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>坦克型</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>射1</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>下</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>并州弓骑</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>10000</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>射手型</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>射2</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>下</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>并州弓骑</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>10000</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>射手型</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>地形角色信息</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>地图标识</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>机关实例</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>效果说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>城墙</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>城墙地形</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>801</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>防御+5，不可穿越</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>城门</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>城门机关</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>802</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>第4回合打开，吕布可召唤增援</t>
+      <c r="G29" s="4" t="inlineStr"/>
+      <c r="H29" s="4" t="inlineStr"/>
+      <c r="I29" s="4" t="inlineStr"/>
+      <c r="J29" s="4" t="inlineStr"/>
+      <c r="K29" s="4" t="inlineStr"/>
+      <c r="L29" s="4" t="inlineStr"/>
+      <c r="M29" s="4" t="inlineStr"/>
+      <c r="N29" s="4" t="inlineStr"/>
+      <c r="O29" s="4" t="inlineStr"/>
+      <c r="P29" s="4" t="inlineStr"/>
+      <c r="Q29" s="4" t="inlineStr"/>
+      <c r="R29" s="4" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>战场</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>平原地形</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>803</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>无加成</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>战场</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>平原地形</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>803</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>无加成</t>
+      <c r="B30" s="4" t="inlineStr"/>
+      <c r="C30" s="4" t="inlineStr"/>
+      <c r="D30" s="4" t="inlineStr"/>
+      <c r="E30" s="4" t="inlineStr"/>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>宝箱</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr"/>
+      <c r="H30" s="4" t="inlineStr"/>
+      <c r="I30" s="4" t="inlineStr"/>
+      <c r="J30" s="4" t="inlineStr"/>
+      <c r="K30" s="4" t="inlineStr"/>
+      <c r="L30" s="4" t="inlineStr"/>
+      <c r="M30" s="4" t="inlineStr"/>
+      <c r="N30" s="4" t="inlineStr"/>
+      <c r="O30" s="4" t="inlineStr"/>
+      <c r="P30" s="4" t="inlineStr"/>
+      <c r="Q30" s="4" t="inlineStr"/>
+      <c r="R30" s="4" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>宝箱</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>隐藏宝箱</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>804</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>内含龙胆亮银枪碎片</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>宝箱</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>隐藏宝箱</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>804</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>击败吕布前可获取，内含龙胆亮银枪碎片</t>
+      <c r="B31" s="4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="J31" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="K31" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L31" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="M31" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N31" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="O31" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="P31" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q31" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="R31" s="4" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="V33" s="5" t="inlineStr">
+        <is>
+          <t>攻略内容</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:Q1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2290,376 +2900,379 @@
   <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>关卡信息 &gt;&gt;&gt;</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>关卡名称</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>三英战吕布</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>关卡备注</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>S240001</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>场景编号</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>初始摄像机</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>等级</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>镜头\动作</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>角色</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>配音</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="1" t="inlineStr">
         <is>
           <t>character</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="1" t="inlineStr">
         <is>
           <t>boxes</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>spine</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="1" t="inlineStr">
         <is>
           <t>L\R</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="1" t="inlineStr">
         <is>
           <t>bgL</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="1" t="inlineStr">
         <is>
           <t>bgR</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>远景推进</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>从关东军营推近虎牢关</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>城门特写</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>城墙上"虎牢关"三字</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>吕布出场</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>吕布</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>关东军听着：谁能取下我吕布首级，这虎牢关便让与他！</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>骑赤兔马出城</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>张飞怒吼</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>张飞</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>呔！三姓家奴，也敢猖狂！</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>从军营冲出</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>关羽跟上</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>关羽</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>三弟，莫要冲动！</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>紧随其后</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>刘备居中</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>刘备</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>云长、翼德，结义之时誓同生死，今日便战个痛快！</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>三人呈品字形</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>吕布兴趣</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>吕布</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>哦？三个一起上？有趣。</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>画戟指向三人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>战斗位置展示</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>镜头拉远显示战场</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>挂点音效</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>备战音效</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:J1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2673,404 +3286,407 @@
   <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>关卡信息 &gt;&gt;&gt;</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>关卡名称</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>三英战吕布</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>关卡备注</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>S240001</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>场景编号</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>初始摄像机</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>等级</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>镜头\动作</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>角色</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>配音</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="1" t="inlineStr">
         <is>
           <t>character</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="1" t="inlineStr">
         <is>
           <t>boxes</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>spine</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="1" t="inlineStr">
         <is>
           <t>L\R</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="1" t="inlineStr">
         <is>
           <t>bgL</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="1" t="inlineStr">
         <is>
           <t>bgR</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>战场远景</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>夕阳下的虎牢关</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>燎原火收枪</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>燎原火</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>（喘息）三十招...还是拿不下他。</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>枪尖滴血</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>刘备走近</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>刘备</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>多谢壮士相救，敢问尊姓大名？</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>抱拳</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>燎原火</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>燎原火</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>无名小卒，不必挂齿。</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>转身欲走</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>关羽开口</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>关羽</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>阁下枪法精湛，绝非无名之辈。</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>青龙偃月刀横持</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>张飞插话</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>张飞</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>就是！比那吕布还厉害几分！</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>蛇矛杵地</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>燎原火停步</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>燎原火</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>...我叫赵云。</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>侧脸</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>分镜特写</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>燎原火</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>后会有期。</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>翻身上马</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>三人目送</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>刘备</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>赵云...好一个赵子龙。</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>望向背影</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>黑屏字幕</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>关东军退兵，虎牢关之战暂告一段落。而燎原火与吕布的宿命，才刚刚开始...</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>史诗音乐起</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:J1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>